--- a/BWI/bestwine_output/bestwine_San Marino.xlsx
+++ b/BWI/bestwine_output/bestwine_San Marino.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA9"/>
+  <dimension ref="A1:AA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1413,6 +1413,99 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Titan Drink Srl</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Titan Drink Srl</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>21230</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>San Marino</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>San Marino</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>San Marino</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2 Strada Prima Gualdaria</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>47890</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.titan-drink.com</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>titandrink@omniway.sm</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>+39 0549 992098</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/titandrink/</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/titan_drink</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>Tamagnini Sara</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tamagnini-sara-028841138/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
